--- a/MilkRun_Data.xlsx
+++ b/MilkRun_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\demo milkrun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157C5192-6B17-4B3E-B670-893D6494A746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A07DE53-828E-470F-8EEA-34B5A25A4D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36" yWindow="48" windowWidth="23004" windowHeight="12192" activeTab="1" xr2:uid="{F8B34925-2B7F-45FF-9FDC-7C4C452947EC}"/>
   </bookViews>
@@ -849,7 +849,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>38</v>

--- a/MilkRun_Data.xlsx
+++ b/MilkRun_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\demo milkrun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A07DE53-828E-470F-8EEA-34B5A25A4D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC13ACB5-859D-4700-A7FA-FD69BFAC16B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36" yWindow="48" windowWidth="23004" windowHeight="12192" activeTab="1" xr2:uid="{F8B34925-2B7F-45FF-9FDC-7C4C452947EC}"/>
   </bookViews>
@@ -849,7 +849,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>38</v>

--- a/MilkRun_Data.xlsx
+++ b/MilkRun_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\demo milkrun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC13ACB5-859D-4700-A7FA-FD69BFAC16B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB28CDF-7135-4807-91F3-16CE710DC295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36" yWindow="48" windowWidth="23004" windowHeight="12192" activeTab="1" xr2:uid="{F8B34925-2B7F-45FF-9FDC-7C4C452947EC}"/>
   </bookViews>
@@ -832,7 +832,7 @@
         <v>34</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>35</v>
